--- a/data/trans_orig/IP31KM10_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM10_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>26045</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19313</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32343</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,05%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>53,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>30637</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21867</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>39444</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>42,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,63%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30362</t>
+          <t>23545</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22739</t>
+          <t>18080</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38628</t>
+          <t>28945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>60998</t>
+          <t>49591</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48694</t>
+          <t>40982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73003</t>
+          <t>57860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,23%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34218</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27920</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40950</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>56,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>46,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>67,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>40763</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>31956</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>49533</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>57,09%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,76%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44245</t>
+          <t>31377</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35979</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51868</t>
+          <t>36842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>85009</t>
+          <t>65595</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>73004</t>
+          <t>57326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97313</t>
+          <t>74204</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>64,42%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53248</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42293</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>64399</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>46,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,79%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>56,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>69180</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>49514</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>103509</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>55,06%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>82,38%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58870</t>
+          <t>42143</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46122</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70051</t>
+          <t>51392</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>128049</t>
+          <t>95390</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>106213</t>
+          <t>81079</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168414</t>
+          <t>110039</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>51,35%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56469</t>
+          <t>61703</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22140</t>
+          <t>50552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>76135</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>67553</t>
+          <t>57190</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56372</t>
+          <t>47941</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80301</t>
+          <t>66338</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>124022</t>
+          <t>118894</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83657</t>
+          <t>104245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>145858</t>
+          <t>133205</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28317</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22227</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33860</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>49,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>59,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17809</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12972</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23461</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>32,06%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>17566</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24683</t>
+          <t>12495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>22503</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48772</t>
+          <t>45883</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39352</t>
+          <t>37763</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57193</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28982</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>23439</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>35072</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>61,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>37743</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>32091</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>42580</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>67,94%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>57,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,65%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>36546</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26945</t>
+          <t>31609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39950</t>
+          <t>41617</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>71413</t>
+          <t>65528</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62992</t>
+          <t>57064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80833</t>
+          <t>73648</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>66,1%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37096</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>27817</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49883</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>53,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>71,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20046</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13587</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27223</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28,77%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30265</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55857</t>
+          <t>29065</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>60672</t>
+          <t>58029</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>48044</t>
+          <t>44243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81369</t>
+          <t>74323</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>32720</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19933</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41999</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>46,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>28,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>49636</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>42459</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56095</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>71,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34741</t>
+          <t>49529</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19510</t>
+          <t>41397</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45102</t>
+          <t>55660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>84377</t>
+          <t>82249</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63680</t>
+          <t>65955</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97005</t>
+          <t>96035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>28015</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>23648</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31863</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>70,78%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>80,51%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>22441</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18246</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26256</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>65,62%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,35%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>29350</t>
+          <t>23151</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>18734</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33402</t>
+          <t>27008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>51791</t>
+          <t>51166</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45622</t>
+          <t>45236</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56977</t>
+          <t>56362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11564</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7716</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>15931</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>29,22%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19,49%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>11759</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>7944</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>15954</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>34,38%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>23,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>46,65%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16125</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>23128</t>
+          <t>23783</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17942</t>
+          <t>18587</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29297</t>
+          <t>29713</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>16232</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>11523</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>21428</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>34,38%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>24,41%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>45,39%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>14534</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>9946</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>19759</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>32,82%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>22,46%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>44,61%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24241</t>
+          <t>20151</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>31144</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40162</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>30977</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>25781</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>35686</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>65,62%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>54,61%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>75,59%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>29756</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>24531</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>34344</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>67,18%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>55,39%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>77,54%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>35363</t>
+          <t>29374</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29541</t>
+          <t>24135</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>33774</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>65118</t>
+          <t>60351</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57910</t>
+          <t>52628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72098</t>
+          <t>66553</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>72,74%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>63515</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>52863</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>74849</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>45,18%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>37,61%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>53,25%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>57463</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>47433</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>67073</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>46,45%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>38,35%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>54,22%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>69768</t>
+          <t>56764</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56629</t>
+          <t>46687</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>82171</t>
+          <t>66023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>127231</t>
+          <t>120279</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>111009</t>
+          <t>105820</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143506</t>
+          <t>135713</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>77056</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>65722</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>87708</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>54,82%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>46,75%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>62,39%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>66233</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>56623</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>76263</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>53,55%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>45,78%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>61,65%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>85276</t>
+          <t>65058</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72873</t>
+          <t>55799</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>98415</t>
+          <t>75135</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>151509</t>
+          <t>142115</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>135234</t>
+          <t>126681</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>167731</t>
+          <t>156574</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>144496</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>137063</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>149778</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>87,23%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>95,32%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>110279</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>102587</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>116190</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>85,71%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>90,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>141462</t>
+          <t>117769</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>134028</t>
+          <t>107569</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>146403</t>
+          <t>124626</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>251740</t>
+          <t>262265</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>241647</t>
+          <t>250915</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>259942</t>
+          <t>270484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>12640</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7358</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>20073</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>18386</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>12475</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>26078</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>20131</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20131</t>
+          <t>30331</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>32771</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22881</t>
+          <t>24552</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41176</t>
+          <t>44121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>396963</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>372106</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>422138</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>57,8%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>54,18%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>61,46%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>459</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>342390</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>317176</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>383688</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>52,42%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>48,56%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>58,75%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>419820</t>
+          <t>316782</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>394361</t>
+          <t>296244</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>449275</t>
+          <t>339309</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>762210</t>
+          <t>713745</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>726618</t>
+          <t>683147</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>811629</t>
+          <t>746073</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>289861</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>264686</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>314718</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>38,54%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>45,82%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>310744</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>269446</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>335958</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>47,58%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>41,25%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>51,44%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>324913</t>
+          <t>301426</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>295458</t>
+          <t>278899</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>350372</t>
+          <t>321964</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>635657</t>
+          <t>591286</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>586238</t>
+          <t>558958</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>671249</t>
+          <t>621884</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,65%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
